--- a/affiliate_data/อาหารและเครื่องดื่ม.xlsx
+++ b/affiliate_data/อาหารและเครื่องดื่ม.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut)</v>
+        <v>น้ำมันถั่วเหลือง ตราองุ่น ขนาด1ลิตร แพ็ค3ขวด โปรโมชั่นสุดคุ้ม</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztg-mnmyv5cdh05e5b.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>195.00</v>
+        <v>182.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 5พัน+ ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/19153594242</v>
+        <v>https://shopee.co.th/product/0/50659706590</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/8fPm8nVF0k</v>
+        <v>https://s.shopee.co.th/7AbMVrSjRr</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -480,37 +480,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】</v>
+        <v>The Chocolate Factory บราวนี่แครกเกอร์ แผ่นกลม รสดาร์กช็อกโกแลต ขนาด 40 กรัม</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztj-mlvtyt7kgburbc.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>1451.00</v>
+        <v>45.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 80 ชิ้น</v>
+        <v>ขายได้ 66 ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/26083508913</v>
+        <v>https://shopee.co.th/product/0/27453231203</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/2Vp8nSwIA9</v>
+        <v>https://s.shopee.co.th/4VabKxlcAB</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -518,13 +518,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g.</v>
+        <v>Ensure Gold AdvancePro wheat เอนชัวร์ โกลด์ แอดวานซ์โปร รสข้าวสาลี ขนาด 800 กรัม(1กระป๋อง)</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mngva2okzpjaca.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>177.00</v>
+        <v>690.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -533,22 +533,22 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 225 ชิ้น</v>
+        <v>ขายได้ 567 ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://shopee.co.th/product/0/46259678621</v>
+        <v>https://shopee.co.th/product/0/55859464305</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/8pjCL6ho1X</v>
+        <v>https://s.shopee.co.th/1LdZZ95AAb</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -556,37 +556,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด 100% | SOURDOUGH BREAD |</v>
+        <v>[พร้อมส่งในไทย]Marukyu Koyamaen Matcha มัทฉะมารุคิวโคยามะเอ็น สาหร่ายผู้ดี อูมามิ เกรดพิธีการญี่ปุ่น</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasj-m91el64l52bt32.webp</v>
       </c>
       <c r="D5" t="str">
-        <v>182.00</v>
+        <v>1118.00</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G5" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 166 ชิ้น</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>https://shopee.co.th/product/0/42859278102</v>
+        <v>https://shopee.co.th/product/0/24294620844</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/9AM2jit34K</v>
+        <v>https://s.shopee.co.th/7pr3J5kKve</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก.</v>
+        <v>หมูสามชั้นแดดเดียวพรีเมี่ยม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง ไม่ใส่สารกันเสีย ทอดง่ายๆใน 5 นาที</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mmfq4vxucrgla3.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>290.00</v>
+        <v>189.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 867 ชิ้น</v>
+        <v>ขายได้ 67 ชิ้น</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/29517921789</v>
+        <v>https://shopee.co.th/product/0/52506367328</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/7pqf9H2jLU</v>
+        <v>https://s.shopee.co.th/8pjaUvq9ci</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -632,37 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89</v>
+        <v>Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด 100% | SOURDOUGH BREAD |</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>99.00</v>
+        <v>182.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>37</v>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 2พัน+ ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/18375829634</v>
+        <v>https://shopee.co.th/product/0/42859278102</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/6VLHYpGKZE</v>
+        <v>https://s.shopee.co.th/W4SZcVdkx</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -670,37 +670,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>น้ำพริกหนังไก่ ยาหยี (100/150/200 ก) 🌶 เผ็ด จัดจ้าน</v>
+        <v>[ยกลัง12ขวด]น้ำมันปาล์ม มรกต และ ทับทิม ขวด 1ลิตร x 12 ขวด น้ำมันพืช มรกต และ ทับทิม</v>
       </c>
       <c r="C8" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r991-lr10flflv2rh60.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81zth-mmixuw8fz18i52.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>75.00</v>
+        <v>893.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 619 ชิ้น</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>https://shopee.co.th/product/0/15598885080</v>
+        <v>https://shopee.co.th/product/0/52658080141</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/50WTm4WhFs</v>
+        <v>https://s.shopee.co.th/2BCgYgRq4z</v>
       </c>
       <c r="K8" t="str">
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -708,37 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร้อมส่งด่วนทั่วประเทศ ซีลแป้งถุงสูญญากาศ</v>
+        <v>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mjebq9kba60z58.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>119.00</v>
+        <v>1451.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 4พัน+ ชิ้น</v>
+        <v>ขายได้ 80 ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/19978484453</v>
+        <v>https://shopee.co.th/product/0/26083508913</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/30lPOOlK3t</v>
+        <v>https://s.shopee.co.th/1VwzlSdFG1</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -746,37 +746,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน</v>
+        <v>Pre-order มาม่าJinmailang (จางหลิงเฮ่อ) แพค</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mni8oy7lbjer1f.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>621.00</v>
+        <v>260.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 7พัน+ ชิ้น</v>
+        <v>ขายได้ 259 ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/14186988359</v>
+        <v>https://shopee.co.th/product/0/52459498202</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/2LVibAwjEv</v>
+        <v>https://s.shopee.co.th/AAEy5OGUk8</v>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>15</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
@@ -784,13 +784,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>ผงมัทฉะ ออร์แกนิค 100% กลิ่นหอมละมุน ชงง่ายในทุกเมนู - RAIWAN ขนาด 100 กรัม</v>
+        <v>หอยจ๊อปูย่าเฮี๊ยะ (เกรดเนื้อหน้าอก)แถมฟรีน้ำจิ้มบ๊วย30ML</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0s-md4csnzellfp52.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mncpondjeg3nd1.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>340.00</v>
+        <v>270.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -799,22 +799,22 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>ขายได้ 901 ชิ้น</v>
+        <v>ขายได้ 2พัน+ ชิ้น</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/42011730902</v>
+        <v>https://shopee.co.th/product/0/15702205781</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/30lPOOyjCD</v>
+        <v>https://s.shopee.co.th/8ATthiVwhF</v>
       </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -822,37 +822,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน 👉 100/200 ก.</v>
+        <v>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lr10flflo1x932.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>109.00</v>
+        <v>822.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>12</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 5พัน+ ชิ้น</v>
       </c>
       <c r="H12" t="str">
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/15587376682</v>
+        <v>https://shopee.co.th/product/0/17396569303</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/60P0xuwNip</v>
+        <v>https://s.shopee.co.th/5fmYj7nmUw</v>
       </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -860,13 +860,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม</v>
+        <v>พร้อมส่งในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ มารุคิวของแท้จากญี่ปุ่น​ Matcha​ มัทฉะยี่ห้อดังจากอูจิ</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mn5j25gwgmx2ed.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>119.00</v>
+        <v>790.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -875,22 +875,22 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 176 ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/17093672460</v>
+        <v>https://shopee.co.th/product/0/40012505165</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/4AxMmYCMnR</v>
+        <v>https://s.shopee.co.th/6ff5uxshlo</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -898,37 +898,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้)</v>
+        <v>ปลาสลิดกรอบ ไร้ก้าง เต็มชิ้น กรอบอร่อย ไม่เหม็นหืน 🐟</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7qula-lhkogxzv71yba0.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>529.00</v>
+        <v>150.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>12</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/24178300700</v>
+        <v>https://shopee.co.th/product/0/21580489912</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/20ssCZUVx7</v>
+        <v>https://s.shopee.co.th/40eKk4DAW1</v>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -939,7 +939,7 @@
         <v>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย</v>
       </c>
       <c r="C15" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</v>
       </c>
       <c r="D15" t="str">
         <v>149.00</v>
@@ -951,7 +951,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 77 ชิ้น</v>
+        <v>ขายได้ 87 ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -960,7 +960,7 @@
         <v>https://shopee.co.th/product/0/54606358747</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/2g8YznZTBU</v>
+        <v>https://s.shopee.co.th/6ff5uyAZwu</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -974,37 +974,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม</v>
+        <v>ไร่พระจันทร์ เมล็ดเจีย chia seed เมล็ดเชีย ธัญพืช มีอย. คัดพิเศษ เกรดพรีเมี่ยม</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98u-lyj1u7grm8w1bb.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>150.00</v>
+        <v>165.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>36</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 6พัน+ ชิ้น</v>
+        <v>ขายได้ 965 ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/21590430844</v>
+        <v>https://shopee.co.th/product/0/24084350655</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/7KuOYNPsuy</v>
+        <v>https://s.shopee.co.th/9030hGB78j</v>
       </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1012,13 +1012,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย</v>
+        <v>น้ำมันมรกต ขนาด 1 ลิตร สำหรับทำอาหาร แพ็ค 3 ขวด | น้ำมันพืชทำอาหาร ผัด ทอด อเนกประสงค์ ใช้ได้ทุกเมนู</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztf-mm9msusd71fnbc.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>129.00</v>
+        <v>280.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1027,22 +1027,22 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 8พัน+ ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/20262305071</v>
+        <v>https://shopee.co.th/product/0/40029535982</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/5q5alcgJru</v>
+        <v>https://s.shopee.co.th/W4SZdljey</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1050,37 +1050,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar)</v>
+        <v>เก๊กฮวยผงสำเร็จรูป HighlandHerb ขนาด 600 กรัม</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>95.00</v>
+        <v>249.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 519 ชิ้น</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/20153592483</v>
+        <v>https://shopee.co.th/product/0/23846377854</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/6fehl9kz4K</v>
+        <v>https://s.shopee.co.th/3B5DkXjty0</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1088,13 +1088,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>สเต็กเนื้อโคขุนพริกไทยดำ(140-150กรัม/ชิ้น)(10ชิ้น)มีทั้งแบบหมักและยังไม่หมัก</v>
+        <v>สลิดติดปาก ปลาสลิดแดดเดียว 5-6 ตัว/โล | ปลาสลิดไข่บางบ่อ ตัวโต สด สะอาด เนื้อแน่นหอมมัน</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-23020-776z5w1itknved.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztm-mgvmi6civ40e0a.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>650.00</v>
+        <v>469.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1103,22 +1103,22 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/2865214924</v>
+        <v>https://shopee.co.th/product/0/29409486599</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/5q5alcwc11</v>
+        <v>https://s.shopee.co.th/4fu1XIoEEN</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1126,13 +1126,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>ปลาหมึกไข่แดดเดียวทอดพร้อมทาน -(ไข่ทุกตัว) ไซร์ 5-9 ตัวต่อแพค น้ำหนักก่อนทอด300กรัมและ 500 กรัม</v>
+        <v>นมกล่อง (ยกลัง) นมยูเอชที นมไฮคิวสูตร3 1พลัส ซูเปอร์โกลด์ รสจืด180 มล (27 กล่อง) นม UHT HiQ Super Gold UHT</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/23e49a44f577b0531100e55e0851f11f.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasg-m7hrtewsksjj0d.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>325.00</v>
+        <v>669.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1141,22 +1141,22 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 214 ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/16667689637</v>
+        <v>https://shopee.co.th/product/0/25842819099</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/6fehlA2J9M</v>
+        <v>https://s.shopee.co.th/3LOdwr0WRj</v>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1164,13 +1164,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ</v>
+        <v>เบอร์ทอลี่น้ำมันมะกอกเอ็กตร้าเวอร์จิน ขนาด500ml.</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mo16o8447m69aa.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>134.00</v>
+        <v>560.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1179,22 +1179,22 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 37 ชิ้น</v>
+        <v>ขายได้ 293 ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/48505914026</v>
+        <v>https://shopee.co.th/product/0/55006004921</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/2qRzC7LIj7</v>
+        <v>https://s.shopee.co.th/9030hGnxIf</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
